--- a/notebook/excel/INSURANCE_PDF_STUFF.xlsx
+++ b/notebook/excel/INSURANCE_PDF_STUFF.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaustubh.keny\Projects\OFFICE PROJECTS\rep_fsparse\notebook\sample_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaustubh.keny\Projects\OFFICE PROJECTS\rep_fsparse\notebook\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9E16C4-6F79-4CA1-899C-E7F59300CA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BDD4AB-ED49-4185-BCDC-612925994CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3956" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3963" uniqueCount="877">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -2648,15 +2648,9 @@
     <t>73_30-Apr-26_IF</t>
   </si>
   <si>
-    <t>Individual</t>
-  </si>
-  <si>
     <t>73_30-Apr-26_1_IF</t>
   </si>
   <si>
-    <t>Group</t>
-  </si>
-  <si>
     <t>ICICI Prudential Life Insurance Fund</t>
   </si>
   <si>
@@ -2673,6 +2667,9 @@
   </si>
   <si>
     <t>Nil</t>
+  </si>
+  <si>
+    <t>Line change</t>
   </si>
 </sst>
 </file>
@@ -2710,7 +2707,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2753,6 +2750,18 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2781,7 +2790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2799,6 +2808,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -27569,122 +27580,109 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="13"/>
+    <col min="4" max="4" width="12.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="13"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>865</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>866</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="G1" s="13" t="s">
+      <c r="D1" s="13" t="s">
+        <v>872</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>874</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="F1" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>73</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D2" t="s">
-        <v>868</v>
-      </c>
-      <c r="E2" t="s">
-        <v>869</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D2" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>74</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="D3" t="s">
-        <v>870</v>
-      </c>
-      <c r="E3" t="s">
-        <v>871</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D3" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>75</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="G4" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D4" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>76</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="G5" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D5" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>77</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="G6" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D6" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>78</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="G7" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>79</v>
       </c>
@@ -27692,79 +27690,82 @@
         <v>361</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>80</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D9" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>81</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D10" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>82</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D11" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>83</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>872</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>870</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>84</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="G13" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D13" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>85</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D14" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>86</v>
       </c>
@@ -27772,45 +27773,63 @@
         <v>626</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>87</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D16" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="F16" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>88</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>647</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D17" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="F17" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>89</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D18" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>90</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="G19" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D19" s="13" t="s">
+        <v>873</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>91</v>
       </c>
@@ -27818,45 +27837,65 @@
         <v>686</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>92</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>712</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D21" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>93</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="17" t="s">
         <v>761</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C22" s="18"/>
+      <c r="D22" s="18" t="s">
+        <v>875</v>
+      </c>
+      <c r="E22" s="18"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>94</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>783</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D23" s="13" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>112</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>873</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>877</v>
+        <v>871</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>869</v>
       </c>
     </row>
   </sheetData>

--- a/notebook/excel/INSURANCE_PDF_STUFF.xlsx
+++ b/notebook/excel/INSURANCE_PDF_STUFF.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaustubh.keny\Projects\OFFICE PROJECTS\rep_fsparse\notebook\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BDD4AB-ED49-4185-BCDC-612925994CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C201CE68-16DE-4A63-A3AB-933952622C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Questionare" sheetId="1" r:id="rId1"/>
     <sheet name="Portfolio Format" sheetId="2" r:id="rId2"/>
     <sheet name="Fund Performance Field List" sheetId="3" r:id="rId3"/>
     <sheet name="Codes" sheetId="4" r:id="rId4"/>
+    <sheet name="CONFIG STYLE" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3963" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3974" uniqueCount="882">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -2670,6 +2671,21 @@
   </si>
   <si>
     <t>Line change</t>
+  </si>
+  <si>
+    <t>AMC_NAME</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>IMP_DATA</t>
+  </si>
+  <si>
+    <t>amc_name</t>
+  </si>
+  <si>
+    <t>mutual_fund_name</t>
   </si>
 </sst>
 </file>
@@ -27620,6 +27636,9 @@
       <c r="E2" s="13" t="s">
         <v>873</v>
       </c>
+      <c r="F2" t="s">
+        <v>873</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
@@ -27631,6 +27650,9 @@
       <c r="D3" s="13" t="s">
         <v>873</v>
       </c>
+      <c r="F3" t="s">
+        <v>873</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
@@ -27642,6 +27664,9 @@
       <c r="D4" s="13" t="s">
         <v>873</v>
       </c>
+      <c r="F4" t="s">
+        <v>873</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
@@ -27656,6 +27681,9 @@
       <c r="E5" s="13" t="s">
         <v>873</v>
       </c>
+      <c r="F5" t="s">
+        <v>873</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -27900,6 +27928,45 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9AFD206-2D51-449F-A11D-365066711800}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>880</v>
+      </c>
+      <c r="B3" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>881</v>
+      </c>
+      <c r="B4" t="s">
+        <v>878</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>